--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名钻 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -855,7 +719,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -901,7 +765,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -947,7 +811,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -993,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1039,7 +903,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1135,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1181,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1227,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1273,7 +1137,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1319,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1415,7 +1279,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1461,7 +1325,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1507,7 +1371,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1553,7 +1417,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1599,7 +1463,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1645,7 +1509,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1741,7 +1605,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1787,7 +1651,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1833,7 +1697,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1879,7 +1743,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1925,7 +1789,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1971,7 +1835,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2017,7 +1881,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2063,7 +1927,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2109,7 +1973,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2155,7 +2019,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2201,7 +2065,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2247,7 +2111,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2293,7 +2157,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2339,7 +2203,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2385,7 +2249,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2431,7 +2295,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2477,7 +2341,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2523,7 +2387,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2569,7 +2433,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2615,7 +2479,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2661,7 +2525,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2707,7 +2571,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2753,7 +2617,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2799,7 +2663,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2845,7 +2709,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2891,7 +2755,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2937,7 +2801,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2983,7 +2847,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3029,7 +2893,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3075,7 +2939,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3121,7 +2985,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3167,7 +3031,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3213,7 +3077,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3259,7 +3123,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3305,7 +3169,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3351,7 +3215,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3397,7 +3261,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3443,7 +3307,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3489,7 +3353,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3535,7 +3399,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3581,7 +3445,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3627,7 +3491,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3673,7 +3537,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3719,7 +3583,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3765,7 +3629,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3811,7 +3675,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3857,7 +3721,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3903,7 +3767,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3949,7 +3813,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3995,7 +3859,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4041,7 +3905,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4087,7 +3951,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4133,7 +3997,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4179,7 +4043,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4225,7 +4089,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4271,7 +4135,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4317,7 +4181,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4363,7 +4227,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4385,881 +4249,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>名钻 - 名钻 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>80 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>74 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1610呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1083呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$2,132万
-$25,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,849万
-$34,694/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$2,488万
-$30,379/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$1,065万
-$25,173/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$1,196万
-$26,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$2,060万
-$25,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,458万
-$27,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$2,065万
-$25,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$1,025万
-$24,222/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$1,477万
-$32,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,987万
-$24,201/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,407万
-$26,392/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,992万
-$24,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$994万
-$23,499/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$1,112万
-$24,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,887万
-$22,981/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,355万
-$25,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$2,866万
-$34,994/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$978万
-$23,118/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,656万
-$24,646/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,838万
-$22,386/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,363万
-$25,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,860万
-$22,709/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$940万
-$22,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$1,010万
-$22,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,585万
-$23,591/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,768万
-$21,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,279万
-$23,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,806万
-$22,048/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$917万
-$21,676/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$980万
-$21,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,539万
-$22,903/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,760万
-$21,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,266万
-$23,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,787万
-$21,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$886万
-$20,943/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$966万
-$21,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,525万
-$22,688/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,731万
-$21,084/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,229万
-$23,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,744万
-$21,298/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$878万
-$20,764/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$938万
-$20,933/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,480万
-$22,027/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,680万
-$20,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,188万
-$22,280/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,685万
-$20,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$844万
-$19,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$906万
-$20,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,430万
-$21,281/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,631万
-$19,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,147万
-$21,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,637万
-$19,984/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$820万
-$19,383/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$902万
-$20,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,384万
-$20,601/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,586万
-$19,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,119万
-$21,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,588万
-$19,389/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$810万
-$19,137/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$858万
-$19,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,356万
-$20,176/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,568万
-$19,093/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,092万
-$20,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,568万
-$19,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$775万
-$18,319/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$839万
-$18,737/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,326万
-$19,735/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 821呎 (3房)
-$1,550万
-$18,884/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 533呎 (2房)
-$1,065万
-$19,989/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 819呎 (3房)
-$1,551万
-$18,933/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 423呎 (2房)
-$755万
-$17,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 448呎 (2房)
-$821万
-$18,319/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 672呎 (3房)
-$1,296万
-$19,289/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名钻" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4249,4 +4428,881 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>名钻 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1610呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1083呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$2132万
+$25,967/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1849万
+$34,694/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$2488万
+$30,379/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$1065万
+$25,173/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$1196万
+$26,708/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$2060万
+$25,090/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1458万
+$27,345/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$2065万
+$25,210/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$1025万
+$24,222/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$1477万
+$32,967/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1987万
+$24,201/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1407万
+$26,392/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1992万
+$24,326/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$994万
+$23,499/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$1112万
+$24,819/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1887万
+$22,981/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1355万
+$25,417/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$2866万
+$34,994/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$978万
+$23,118/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1656万
+$24,646/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1838万
+$22,386/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1363万
+$25,578/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1860万
+$22,709/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$940万
+$22,227/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$1010万
+$22,533/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1585万
+$23,591/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1768万
+$21,541/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1279万
+$23,991/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1806万
+$22,048/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$917万
+$21,676/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$980万
+$21,877/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1539万
+$22,903/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1760万
+$21,437/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1266万
+$23,750/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1787万
+$21,823/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$886万
+$20,943/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$966万
+$21,560/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1525万
+$22,688/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1731万
+$21,084/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1229万
+$23,060/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1744万
+$21,298/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$878万
+$20,764/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$938万
+$20,933/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1480万
+$22,027/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1680万
+$20,458/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1188万
+$22,280/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1685万
+$20,578/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$844万
+$19,965/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$906万
+$20,225/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1430万
+$21,281/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1631万
+$19,861/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1147万
+$21,525/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1637万
+$19,984/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$820万
+$19,383/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$902万
+$20,127/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1384万
+$20,601/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1586万
+$19,322/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1119万
+$21,000/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1588万
+$19,389/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$810万
+$19,137/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$858万
+$19,141/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1356万
+$20,176/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1568万
+$19,093/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1092万
+$20,488/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1568万
+$19,140/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$775万
+$18,319/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$839万
+$18,737/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1326万
+$19,735/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 821呎 (3房)
+$1550万
+$18,884/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 533呎 (2房)
+$1065万
+$19,989/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 819呎 (3房)
+$1551万
+$18,933/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 423呎 (2房)
+$755万
+$17,839/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 448呎 (2房)
+$821万
+$18,319/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 672呎 (3房)
+$1296万
+$19,289/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -909,6 +993,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -955,6 +1059,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1001,6 +1125,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1047,6 +1191,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1093,6 +1257,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1143,6 +1327,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1189,6 +1393,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1235,6 +1459,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1281,6 +1525,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1327,6 +1591,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1373,6 +1657,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1423,6 +1727,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1469,6 +1793,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1515,6 +1859,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1561,6 +1925,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1607,6 +1991,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1653,6 +2057,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1699,6 +2123,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1749,6 +2193,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1795,6 +2259,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1841,6 +2325,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1887,6 +2391,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1933,6 +2457,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1979,6 +2523,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2025,6 +2589,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2071,6 +2655,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2117,6 +2721,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2163,6 +2787,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2209,6 +2853,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2255,6 +2919,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2301,6 +2985,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2347,6 +3051,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2393,6 +3117,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2439,6 +3183,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2485,6 +3249,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2531,6 +3315,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2577,6 +3381,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2623,6 +3447,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2669,6 +3513,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2715,6 +3579,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2761,6 +3645,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2807,6 +3711,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2853,6 +3777,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2899,6 +3843,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2945,6 +3909,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2991,6 +3975,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3037,6 +4041,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3083,6 +4107,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3129,6 +4173,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3175,6 +4239,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3221,6 +4305,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3267,6 +4371,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3313,6 +4437,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3359,6 +4503,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3405,6 +4569,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3451,6 +4635,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3497,6 +4701,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3543,6 +4767,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3589,6 +4833,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3635,6 +4899,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3681,6 +4965,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3727,6 +5031,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3773,6 +5097,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3819,6 +5163,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3865,6 +5229,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3911,6 +5295,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3957,6 +5361,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4003,6 +5427,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4049,6 +5493,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4095,6 +5559,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4141,6 +5625,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4187,6 +5691,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4233,6 +5757,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4279,6 +5823,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4325,6 +5889,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4371,6 +5955,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4417,13 +6021,33 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4594,7 +6218,7 @@
           <t>A | 821呎 (3房)
 $2132万
 $25,967/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -4602,7 +6226,7 @@
           <t>B | 533呎 (2房)
 $1849万
 $34,694/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -4610,7 +6234,7 @@
           <t>C | 819呎 (3房)
 $2488万
 $30,379/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -4618,7 +6242,7 @@
           <t>D | 423呎 (2房)
 $1065万
 $25,173/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -4626,7 +6250,7 @@
           <t>E | 448呎 (2房)
 $1196万
 $26,708/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -4649,7 +6273,7 @@
           <t>A | 821呎 (3房)
 $2060万
 $25,090/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4657,7 +6281,7 @@
           <t>B | 533呎 (2房)
 $1458万
 $27,345/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -4665,7 +6289,7 @@
           <t>C | 819呎 (3房)
 $2065万
 $25,210/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -4673,7 +6297,7 @@
           <t>D | 423呎 (2房)
 $1025万
 $24,222/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -4681,7 +6305,7 @@
           <t>E | 448呎 (2房)
 $1477万
 $32,967/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -4704,7 +6328,7 @@
           <t>A | 821呎 (3房)
 $1987万
 $24,201/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -4712,7 +6336,7 @@
           <t>B | 533呎 (2房)
 $1407万
 $26,392/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -4720,7 +6344,7 @@
           <t>C | 819呎 (3房)
 $1992万
 $24,326/呎
-(25年-01月)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -4728,7 +6352,7 @@
           <t>D | 423呎 (2房)
 $994万
 $23,499/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -4736,7 +6360,7 @@
           <t>E | 448呎 (2房)
 $1112万
 $24,819/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -4759,7 +6383,7 @@
           <t>A | 821呎 (3房)
 $1887万
 $22,981/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -4767,7 +6391,7 @@
           <t>B | 533呎 (2房)
 $1355万
 $25,417/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -4775,7 +6399,7 @@
           <t>C | 819呎 (3房)
 $2866万
 $34,994/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -4783,7 +6407,7 @@
           <t>D | 423呎 (2房)
 $978万
 $23,118/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -4799,7 +6423,7 @@
           <t>F | 672呎 (3房)
 $1656万
 $24,646/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -4814,7 +6438,7 @@
           <t>A | 821呎 (3房)
 $1838万
 $22,386/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -4822,7 +6446,7 @@
           <t>B | 533呎 (2房)
 $1363万
 $25,578/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -4830,7 +6454,7 @@
           <t>C | 819呎 (3房)
 $1860万
 $22,709/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4838,7 +6462,7 @@
           <t>D | 423呎 (2房)
 $940万
 $22,227/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -4846,7 +6470,7 @@
           <t>E | 448呎 (2房)
 $1010万
 $22,533/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -4854,7 +6478,7 @@
           <t>F | 672呎 (3房)
 $1585万
 $23,591/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -4869,7 +6493,7 @@
           <t>A | 821呎 (3房)
 $1768万
 $21,541/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -4877,7 +6501,7 @@
           <t>B | 533呎 (2房)
 $1279万
 $23,991/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -4885,7 +6509,7 @@
           <t>C | 819呎 (3房)
 $1806万
 $22,048/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -4893,7 +6517,7 @@
           <t>D | 423呎 (2房)
 $917万
 $21,676/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -4901,7 +6525,7 @@
           <t>E | 448呎 (2房)
 $980万
 $21,877/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -4909,7 +6533,7 @@
           <t>F | 672呎 (3房)
 $1539万
 $22,903/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -4924,7 +6548,7 @@
           <t>A | 821呎 (3房)
 $1760万
 $21,437/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -4932,7 +6556,7 @@
           <t>B | 533呎 (2房)
 $1266万
 $23,750/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -4940,7 +6564,7 @@
           <t>C | 819呎 (3房)
 $1787万
 $21,823/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -4948,7 +6572,7 @@
           <t>D | 423呎 (2房)
 $886万
 $20,943/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -4956,7 +6580,7 @@
           <t>E | 448呎 (2房)
 $966万
 $21,560/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -4964,7 +6588,7 @@
           <t>F | 672呎 (3房)
 $1525万
 $22,688/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -4979,7 +6603,7 @@
           <t>A | 821呎 (3房)
 $1731万
 $21,084/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -4987,7 +6611,7 @@
           <t>B | 533呎 (2房)
 $1229万
 $23,060/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -4995,7 +6619,7 @@
           <t>C | 819呎 (3房)
 $1744万
 $21,298/呎
-(25年-01月)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -5003,7 +6627,7 @@
           <t>D | 423呎 (2房)
 $878万
 $20,764/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -5011,7 +6635,7 @@
           <t>E | 448呎 (2房)
 $938万
 $20,933/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -5019,7 +6643,7 @@
           <t>F | 672呎 (3房)
 $1480万
 $22,027/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +6658,7 @@
           <t>A | 821呎 (3房)
 $1680万
 $20,458/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5042,7 +6666,7 @@
           <t>B | 533呎 (2房)
 $1188万
 $22,280/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5050,7 +6674,7 @@
           <t>C | 819呎 (3房)
 $1685万
 $20,578/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -5058,7 +6682,7 @@
           <t>D | 423呎 (2房)
 $844万
 $19,965/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -5066,7 +6690,7 @@
           <t>E | 448呎 (2房)
 $906万
 $20,225/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -5074,7 +6698,7 @@
           <t>F | 672呎 (3房)
 $1430万
 $21,281/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -5089,7 +6713,7 @@
           <t>A | 821呎 (3房)
 $1631万
 $19,861/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5097,7 +6721,7 @@
           <t>B | 533呎 (2房)
 $1147万
 $21,525/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5105,7 +6729,7 @@
           <t>C | 819呎 (3房)
 $1637万
 $19,984/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -5113,7 +6737,7 @@
           <t>D | 423呎 (2房)
 $820万
 $19,383/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -5121,7 +6745,7 @@
           <t>E | 448呎 (2房)
 $902万
 $20,127/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -5129,7 +6753,7 @@
           <t>F | 672呎 (3房)
 $1384万
 $20,601/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -5144,7 +6768,7 @@
           <t>A | 821呎 (3房)
 $1586万
 $19,322/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5152,7 +6776,7 @@
           <t>B | 533呎 (2房)
 $1119万
 $21,000/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5160,7 +6784,7 @@
           <t>C | 819呎 (3房)
 $1588万
 $19,389/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -5168,7 +6792,7 @@
           <t>D | 423呎 (2房)
 $810万
 $19,137/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -5176,7 +6800,7 @@
           <t>E | 448呎 (2房)
 $858万
 $19,141/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -5184,7 +6808,7 @@
           <t>F | 672呎 (3房)
 $1356万
 $20,176/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -5199,7 +6823,7 @@
           <t>A | 821呎 (3房)
 $1568万
 $19,093/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5207,7 +6831,7 @@
           <t>B | 533呎 (2房)
 $1092万
 $20,488/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5215,7 +6839,7 @@
           <t>C | 819呎 (3房)
 $1568万
 $19,140/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -5223,7 +6847,7 @@
           <t>D | 423呎 (2房)
 $775万
 $18,319/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -5231,7 +6855,7 @@
           <t>E | 448呎 (2房)
 $839万
 $18,737/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -5239,7 +6863,7 @@
           <t>F | 672呎 (3房)
 $1326万
 $19,735/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -5254,7 +6878,7 @@
           <t>A | 821呎 (3房)
 $1550万
 $18,884/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5262,7 +6886,7 @@
           <t>B | 533呎 (2房)
 $1065万
 $19,989/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5270,7 +6894,7 @@
           <t>C | 819呎 (3房)
 $1551万
 $18,933/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -5278,7 +6902,7 @@
           <t>D | 423呎 (2房)
 $755万
 $17,839/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -5286,7 +6910,7 @@
           <t>E | 448呎 (2房)
 $821万
 $18,319/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -5294,7 +6918,7 @@
           <t>F | 672呎 (3房)
 $1296万
 $19,289/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -6218,7 +6218,7 @@
           <t>A | 821呎 (3房)
 $2132万
 $25,967/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6226,7 +6226,7 @@
           <t>B | 533呎 (2房)
 $1849万
 $34,694/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6234,7 +6234,7 @@
           <t>C | 819呎 (3房)
 $2488万
 $30,379/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6242,7 +6242,7 @@
           <t>D | 423呎 (2房)
 $1065万
 $25,173/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -6250,7 +6250,7 @@
           <t>E | 448呎 (2房)
 $1196万
 $26,708/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -6273,7 +6273,7 @@
           <t>A | 821呎 (3房)
 $2060万
 $25,090/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6281,7 +6281,7 @@
           <t>B | 533呎 (2房)
 $1458万
 $27,345/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6289,7 +6289,7 @@
           <t>C | 819呎 (3房)
 $2065万
 $25,210/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6297,7 +6297,7 @@
           <t>D | 423呎 (2房)
 $1025万
 $24,222/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -6305,7 +6305,7 @@
           <t>E | 448呎 (2房)
 $1477万
 $32,967/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -6328,7 +6328,7 @@
           <t>A | 821呎 (3房)
 $1987万
 $24,201/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6336,7 +6336,7 @@
           <t>B | 533呎 (2房)
 $1407万
 $26,392/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6344,7 +6344,7 @@
           <t>C | 819呎 (3房)
 $1992万
 $24,326/呎
-(25年-01月-15日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6352,7 +6352,7 @@
           <t>D | 423呎 (2房)
 $994万
 $23,499/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>E | 448呎 (2房)
 $1112万
 $24,819/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -6383,7 +6383,7 @@
           <t>A | 821呎 (3房)
 $1887万
 $22,981/呎
-(25年-03月-03日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6391,7 +6391,7 @@
           <t>B | 533呎 (2房)
 $1355万
 $25,417/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -6399,7 +6399,7 @@
           <t>C | 819呎 (3房)
 $2866万
 $34,994/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -6407,7 +6407,7 @@
           <t>D | 423呎 (2房)
 $978万
 $23,118/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>F | 672呎 (3房)
 $1656万
 $24,646/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
           <t>A | 821呎 (3房)
 $1838万
 $22,386/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6446,7 +6446,7 @@
           <t>B | 533呎 (2房)
 $1363万
 $25,578/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6454,7 +6454,7 @@
           <t>C | 819呎 (3房)
 $1860万
 $22,709/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6462,7 +6462,7 @@
           <t>D | 423呎 (2房)
 $940万
 $22,227/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -6470,7 +6470,7 @@
           <t>E | 448呎 (2房)
 $1010万
 $22,533/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -6478,7 +6478,7 @@
           <t>F | 672呎 (3房)
 $1585万
 $23,591/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
           <t>A | 821呎 (3房)
 $1768万
 $21,541/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6501,7 +6501,7 @@
           <t>B | 533呎 (2房)
 $1279万
 $23,991/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>C | 819呎 (3房)
 $1806万
 $22,048/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6517,7 +6517,7 @@
           <t>D | 423呎 (2房)
 $917万
 $21,676/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -6525,7 +6525,7 @@
           <t>E | 448呎 (2房)
 $980万
 $21,877/呎
-(24年-12月-17日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -6533,7 +6533,7 @@
           <t>F | 672呎 (3房)
 $1539万
 $22,903/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
           <t>A | 821呎 (3房)
 $1760万
 $21,437/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6556,7 +6556,7 @@
           <t>B | 533呎 (2房)
 $1266万
 $23,750/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6564,7 +6564,7 @@
           <t>C | 819呎 (3房)
 $1787万
 $21,823/呎
-(25年-02月-25日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6572,7 +6572,7 @@
           <t>D | 423呎 (2房)
 $886万
 $20,943/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6580,7 +6580,7 @@
           <t>E | 448呎 (2房)
 $966万
 $21,560/呎
-(24年-12月-22日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -6588,7 +6588,7 @@
           <t>F | 672呎 (3房)
 $1525万
 $22,688/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
           <t>A | 821呎 (3房)
 $1731万
 $21,084/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6611,7 +6611,7 @@
           <t>B | 533呎 (2房)
 $1229万
 $23,060/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6619,7 +6619,7 @@
           <t>C | 819呎 (3房)
 $1744万
 $21,298/呎
-(25年-01月-08日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6627,7 +6627,7 @@
           <t>D | 423呎 (2房)
 $878万
 $20,764/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6635,7 +6635,7 @@
           <t>E | 448呎 (2房)
 $938万
 $20,933/呎
-(24年-12月-12日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -6643,7 +6643,7 @@
           <t>F | 672呎 (3房)
 $1480万
 $22,027/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
           <t>A | 821呎 (3房)
 $1680万
 $20,458/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>B | 533呎 (2房)
 $1188万
 $22,280/呎
-(25年-02月-27日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>C | 819呎 (3房)
 $1685万
 $20,578/呎
-(24年-12月-22日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6682,7 +6682,7 @@
           <t>D | 423呎 (2房)
 $844万
 $19,965/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6690,7 +6690,7 @@
           <t>E | 448呎 (2房)
 $906万
 $20,225/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>F | 672呎 (3房)
 $1430万
 $21,281/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
           <t>A | 821呎 (3房)
 $1631万
 $19,861/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -6721,7 +6721,7 @@
           <t>B | 533呎 (2房)
 $1147万
 $21,525/呎
-(24年-12月-17日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -6729,7 +6729,7 @@
           <t>C | 819呎 (3房)
 $1637万
 $19,984/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -6737,7 +6737,7 @@
           <t>D | 423呎 (2房)
 $820万
 $19,383/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -6745,7 +6745,7 @@
           <t>E | 448呎 (2房)
 $902万
 $20,127/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -6753,7 +6753,7 @@
           <t>F | 672呎 (3房)
 $1384万
 $20,601/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
           <t>A | 821呎 (3房)
 $1586万
 $19,322/呎
-(25年-01月-14日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6776,7 +6776,7 @@
           <t>B | 533呎 (2房)
 $1119万
 $21,000/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6784,7 +6784,7 @@
           <t>C | 819呎 (3房)
 $1588万
 $19,389/呎
-(25年-01月-05日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6792,7 +6792,7 @@
           <t>D | 423呎 (2房)
 $810万
 $19,137/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6800,7 +6800,7 @@
           <t>E | 448呎 (2房)
 $858万
 $19,141/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -6808,7 +6808,7 @@
           <t>F | 672呎 (3房)
 $1356万
 $20,176/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
           <t>A | 821呎 (3房)
 $1568万
 $19,093/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6831,7 +6831,7 @@
           <t>B | 533呎 (2房)
 $1092万
 $20,488/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6839,7 +6839,7 @@
           <t>C | 819呎 (3房)
 $1568万
 $19,140/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6847,7 +6847,7 @@
           <t>D | 423呎 (2房)
 $775万
 $18,319/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6855,7 +6855,7 @@
           <t>E | 448呎 (2房)
 $839万
 $18,737/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -6863,7 +6863,7 @@
           <t>F | 672呎 (3房)
 $1326万
 $19,735/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
           <t>A | 821呎 (3房)
 $1550万
 $18,884/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6886,7 +6886,7 @@
           <t>B | 533呎 (2房)
 $1065万
 $19,989/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -6894,7 +6894,7 @@
           <t>C | 819呎 (3房)
 $1551万
 $18,933/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -6902,7 +6902,7 @@
           <t>D | 423呎 (2房)
 $755万
 $17,839/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -6910,7 +6910,7 @@
           <t>E | 448呎 (2房)
 $821万
 $18,319/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -6918,7 +6918,7 @@
           <t>F | 672呎 (3房)
 $1296万
 $19,289/呎
-(24年-12月-23日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -6218,7 +6218,7 @@
           <t>A | 821呎 (3房)
 $2132万
 $25,967/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6226,7 +6226,7 @@
           <t>B | 533呎 (2房)
 $1849万
 $34,694/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6234,7 +6234,7 @@
           <t>C | 819呎 (3房)
 $2488万
 $30,379/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6242,7 +6242,7 @@
           <t>D | 423呎 (2房)
 $1065万
 $25,173/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -6250,7 +6250,7 @@
           <t>E | 448呎 (2房)
 $1196万
 $26,708/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -6273,7 +6273,7 @@
           <t>A | 821呎 (3房)
 $2060万
 $25,090/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6281,7 +6281,7 @@
           <t>B | 533呎 (2房)
 $1458万
 $27,345/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6289,7 +6289,7 @@
           <t>C | 819呎 (3房)
 $2065万
 $25,210/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6297,7 +6297,7 @@
           <t>D | 423呎 (2房)
 $1025万
 $24,222/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -6305,7 +6305,7 @@
           <t>E | 448呎 (2房)
 $1477万
 $32,967/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -6328,7 +6328,7 @@
           <t>A | 821呎 (3房)
 $1987万
 $24,201/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6336,7 +6336,7 @@
           <t>B | 533呎 (2房)
 $1407万
 $26,392/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6344,7 +6344,7 @@
           <t>C | 819呎 (3房)
 $1992万
 $24,326/呎
-(25年-01月)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6352,7 +6352,7 @@
           <t>D | 423呎 (2房)
 $994万
 $23,499/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>E | 448呎 (2房)
 $1112万
 $24,819/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -6383,7 +6383,7 @@
           <t>A | 821呎 (3房)
 $1887万
 $22,981/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6391,7 +6391,7 @@
           <t>B | 533呎 (2房)
 $1355万
 $25,417/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -6399,7 +6399,7 @@
           <t>C | 819呎 (3房)
 $2866万
 $34,994/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -6407,7 +6407,7 @@
           <t>D | 423呎 (2房)
 $978万
 $23,118/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>F | 672呎 (3房)
 $1656万
 $24,646/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
           <t>A | 821呎 (3房)
 $1838万
 $22,386/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6446,7 +6446,7 @@
           <t>B | 533呎 (2房)
 $1363万
 $25,578/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6454,7 +6454,7 @@
           <t>C | 819呎 (3房)
 $1860万
 $22,709/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6462,7 +6462,7 @@
           <t>D | 423呎 (2房)
 $940万
 $22,227/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -6470,7 +6470,7 @@
           <t>E | 448呎 (2房)
 $1010万
 $22,533/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -6478,7 +6478,7 @@
           <t>F | 672呎 (3房)
 $1585万
 $23,591/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
           <t>A | 821呎 (3房)
 $1768万
 $21,541/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6501,7 +6501,7 @@
           <t>B | 533呎 (2房)
 $1279万
 $23,991/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>C | 819呎 (3房)
 $1806万
 $22,048/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6517,7 +6517,7 @@
           <t>D | 423呎 (2房)
 $917万
 $21,676/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -6525,7 +6525,7 @@
           <t>E | 448呎 (2房)
 $980万
 $21,877/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -6533,7 +6533,7 @@
           <t>F | 672呎 (3房)
 $1539万
 $22,903/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
           <t>A | 821呎 (3房)
 $1760万
 $21,437/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6556,7 +6556,7 @@
           <t>B | 533呎 (2房)
 $1266万
 $23,750/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6564,7 +6564,7 @@
           <t>C | 819呎 (3房)
 $1787万
 $21,823/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6572,7 +6572,7 @@
           <t>D | 423呎 (2房)
 $886万
 $20,943/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6580,7 +6580,7 @@
           <t>E | 448呎 (2房)
 $966万
 $21,560/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -6588,7 +6588,7 @@
           <t>F | 672呎 (3房)
 $1525万
 $22,688/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
           <t>A | 821呎 (3房)
 $1731万
 $21,084/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6611,7 +6611,7 @@
           <t>B | 533呎 (2房)
 $1229万
 $23,060/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6619,7 +6619,7 @@
           <t>C | 819呎 (3房)
 $1744万
 $21,298/呎
-(25年-01月)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6627,7 +6627,7 @@
           <t>D | 423呎 (2房)
 $878万
 $20,764/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6635,7 +6635,7 @@
           <t>E | 448呎 (2房)
 $938万
 $20,933/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -6643,7 +6643,7 @@
           <t>F | 672呎 (3房)
 $1480万
 $22,027/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
           <t>A | 821呎 (3房)
 $1680万
 $20,458/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>B | 533呎 (2房)
 $1188万
 $22,280/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>C | 819呎 (3房)
 $1685万
 $20,578/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6682,7 +6682,7 @@
           <t>D | 423呎 (2房)
 $844万
 $19,965/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6690,7 +6690,7 @@
           <t>E | 448呎 (2房)
 $906万
 $20,225/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>F | 672呎 (3房)
 $1430万
 $21,281/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
           <t>A | 821呎 (3房)
 $1631万
 $19,861/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -6721,7 +6721,7 @@
           <t>B | 533呎 (2房)
 $1147万
 $21,525/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -6729,7 +6729,7 @@
           <t>C | 819呎 (3房)
 $1637万
 $19,984/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -6737,7 +6737,7 @@
           <t>D | 423呎 (2房)
 $820万
 $19,383/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -6745,7 +6745,7 @@
           <t>E | 448呎 (2房)
 $902万
 $20,127/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -6753,7 +6753,7 @@
           <t>F | 672呎 (3房)
 $1384万
 $20,601/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
           <t>A | 821呎 (3房)
 $1586万
 $19,322/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6776,7 +6776,7 @@
           <t>B | 533呎 (2房)
 $1119万
 $21,000/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6784,7 +6784,7 @@
           <t>C | 819呎 (3房)
 $1588万
 $19,389/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6792,7 +6792,7 @@
           <t>D | 423呎 (2房)
 $810万
 $19,137/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6800,7 +6800,7 @@
           <t>E | 448呎 (2房)
 $858万
 $19,141/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -6808,7 +6808,7 @@
           <t>F | 672呎 (3房)
 $1356万
 $20,176/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
           <t>A | 821呎 (3房)
 $1568万
 $19,093/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6831,7 +6831,7 @@
           <t>B | 533呎 (2房)
 $1092万
 $20,488/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6839,7 +6839,7 @@
           <t>C | 819呎 (3房)
 $1568万
 $19,140/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6847,7 +6847,7 @@
           <t>D | 423呎 (2房)
 $775万
 $18,319/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6855,7 +6855,7 @@
           <t>E | 448呎 (2房)
 $839万
 $18,737/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -6863,7 +6863,7 @@
           <t>F | 672呎 (3房)
 $1326万
 $19,735/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
           <t>A | 821呎 (3房)
 $1550万
 $18,884/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6886,7 +6886,7 @@
           <t>B | 533呎 (2房)
 $1065万
 $19,989/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -6894,7 +6894,7 @@
           <t>C | 819呎 (3房)
 $1551万
 $18,933/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -6902,7 +6902,7 @@
           <t>D | 423呎 (2房)
 $755万
 $17,839/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -6910,7 +6910,7 @@
           <t>E | 448呎 (2房)
 $821万
 $18,319/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -6918,7 +6918,7 @@
           <t>F | 672呎 (3房)
 $1296万
 $19,289/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
     </row>
